--- a/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importQqchAppInnovatePlan.xlsx
+++ b/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importQqchAppInnovatePlan.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26529"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\韩\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\folder\folder-work\hhwy\project\zj\opmp\opmp\Ft-Cloud\ft-services\ft-service-pm\src\main\resources\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6730F381-E0C1-4101-BFB0-377BE17B17D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CDB48FA-DC95-432A-8993-780C0D715F32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -491,6 +491,11 @@
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
+  <dataValidations count="1">
+    <dataValidation type="date" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="日期格式错误！" sqref="D1:D1048576 E1:E1048576" xr:uid="{39E574A8-2FCE-4E8C-8E63-401D12288B1D}">
+      <formula1>1</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importQqchAppInnovatePlan.xlsx
+++ b/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importQqchAppInnovatePlan.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\folder\folder-work\hhwy\project\zj\opmp\opmp\Ft-Cloud\ft-services\ft-service-pm\src\main\resources\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CDB48FA-DC95-432A-8993-780C0D715F32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6956A41-B46F-46BC-BC41-116E911C87F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3010" yWindow="1910" windowWidth="19080" windowHeight="11150" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2023-07-28" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>“四新”技术名称</t>
   </si>
@@ -48,6 +48,10 @@
   </si>
   <si>
     <t>four_news_type</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>注：开始时间不能晚于结束时间</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -55,7 +59,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -80,6 +84,13 @@
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -125,7 +136,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -134,6 +145,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -449,13 +463,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="6" width="16.75" customWidth="1"/>
+    <col min="8" max="8" width="33.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -475,7 +490,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -487,6 +502,9 @@
       <c r="E2" s="1"/>
       <c r="F2" s="1" t="s">
         <v>6</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importQqchAppInnovatePlan.xlsx
+++ b/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importQqchAppInnovatePlan.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\folder\folder-work\hhwy\project\zj\opmp\opmp\Ft-Cloud\ft-services\ft-service-pm\src\main\resources\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6956A41-B46F-46BC-BC41-116E911C87F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7629DAD6-11BA-445E-828E-937919152F9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3010" yWindow="1910" windowWidth="19080" windowHeight="11150" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2023-07-28" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -91,6 +91,14 @@
       <color rgb="FFFF0000"/>
       <name val="等线"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -136,7 +144,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -147,6 +155,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -489,6 +500,9 @@
       <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
+      <c r="H1" s="4" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="2" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -503,9 +517,7 @@
       <c r="F2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="H2" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
